--- a/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-4B-Instruct-2507/metrics_default_vs_simple.xlsx
+++ b/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-4B-Instruct-2507/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.6896551724137931</v>
+        <v>0.6829268292682927</v>
       </c>
       <c r="B2">
-        <v>0.02777777777777778</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.5633802816901409</v>
+        <v>0.5704225352112676</v>
       </c>
       <c r="D2">
-        <v>0.5040650406504065</v>
+        <v>0.5213675213675214</v>
       </c>
       <c r="E2">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="F2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G2">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
